--- a/dcf/PANW.xlsx
+++ b/dcf/PANW.xlsx
@@ -361,97 +361,97 @@
   <commentList>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B21" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C21" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B22" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C22" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0" shapeId="0">
       <text>
-        <t>builder default — last-year capex +10% unless set to guidance; edits not tracked</t>
+        <t>workbook (synced) — last-year capex +10% unless set to guidance; edits not tracked</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B44" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>Opus: 14.3x</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C52" authorId="0" shapeId="0">
@@ -887,7 +887,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>builder defaults (consensus-anchored; no Opus pass)</t>
+          <t>Opus 4.8 — values as of 2026-07-06 (provenance seeded)</t>
         </is>
       </c>
     </row>
@@ -1142,184 +1142,184 @@
     </row>
     <row r="5">
       <c r="A5" s="52" t="n">
-        <v>9</v>
+        <v>11.3</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>67.15410060075534</v>
+        <v>76.56378446538642</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>64.82889694002861</v>
+        <v>73.80705422911194</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>62.61208731546802</v>
+        <v>71.1803870278482</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>60.49799297195262</v>
+        <v>68.67692249703781</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>58.48126081557536</v>
+        <v>66.29019541904181</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>56.55684323416383</v>
+        <v>64.01411116304669</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>54.71997925773265</v>
+        <v>61.84292275946744</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="52" t="n">
-        <v>10</v>
+        <v>12.3</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>71.24526749842103</v>
+        <v>80.65495136305209</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>68.73244358745616</v>
+        <v>77.71060087653947</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>66.33743501650288</v>
+        <v>74.90573472888306</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>64.05404928720705</v>
+        <v>72.23297881229223</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>61.87644977360425</v>
+        <v>69.6853843770707</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>59.79913363802594</v>
+        <v>67.25640156690879</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>57.81691121500864</v>
+        <v>64.93985471674343</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="52" t="n">
-        <v>11</v>
+        <v>13.3</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>75.33643439608672</v>
+        <v>84.74611826071778</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>72.63599023488368</v>
+        <v>81.61414752396701</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>70.06278271753774</v>
+        <v>78.63108242991791</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>67.61010560246147</v>
+        <v>75.78903512754668</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>65.27163873163315</v>
+        <v>73.0805733350996</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>63.04142404188804</v>
+        <v>70.49869197077091</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>60.91384317228464</v>
+        <v>68.03678667401942</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="52" t="n">
-        <v>12</v>
+        <v>14.3</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>79.42760129375239</v>
+        <v>88.83728515838345</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>76.53953688231121</v>
+        <v>85.51769417139452</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>73.78813041857259</v>
+        <v>82.35643013095277</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>71.16616191771591</v>
+        <v>79.34509144280111</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>68.66682768966203</v>
+        <v>76.47576229312848</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>66.28371444575015</v>
+        <v>73.74098237463301</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>64.01077512956063</v>
+        <v>71.13371863129542</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
-        <v>13</v>
+        <v>15.3</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>83.51876819141808</v>
+        <v>92.92845205604914</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>80.44308352973874</v>
+        <v>89.42124081882206</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>77.51347811960746</v>
+        <v>86.08177783198764</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>74.72221823297035</v>
+        <v>82.90114775805554</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>72.06201664769092</v>
+        <v>79.87095125115738</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>69.52600484961228</v>
+        <v>76.98327277849512</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>67.10770708683663</v>
+        <v>74.23065058857142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
-        <v>14</v>
+        <v>16.3</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>87.60993508908375</v>
+        <v>97.01961895371481</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>84.34663017716629</v>
+        <v>93.3247874662496</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>81.23882582064232</v>
+        <v>89.8071255330225</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>78.27827454822479</v>
+        <v>86.45720407330997</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>75.45720560571982</v>
+        <v>83.26614020918628</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>72.76829525347439</v>
+        <v>80.22556318235723</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>70.20463904411262</v>
+        <v>77.32758254584742</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
-        <v>15</v>
+        <v>17.3</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>91.70110198674942</v>
+        <v>101.1107858513805</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>88.25017682459379</v>
+        <v>97.22833411367714</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>84.96417352167718</v>
+        <v>93.53247323405736</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>81.83433086347921</v>
+        <v>90.0132603885644</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>78.8523945637487</v>
+        <v>86.66132916721517</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>76.01058565733649</v>
+        <v>83.46785358621936</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>73.30157100138861</v>
+        <v>80.42451450312339</v>
       </c>
     </row>
     <row r="13">
@@ -1342,7 +1342,7 @@
         <v>0.07758496628528873</v>
       </c>
       <c r="C14" s="56" t="n">
-        <v>12</v>
+        <v>14.3</v>
       </c>
     </row>
   </sheetData>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.7815530385558973</v>
+        <v>0.7741892597276353</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24421,7 +24421,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="46">
@@ -24618,13 +24618,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>71.16616191771591</v>
+        <v>79.34509144280111</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>98.75105070539584</v>
+        <v>109.4365782375633</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>51.00505648173939</v>
+        <v>57.18820422515071</v>
       </c>
     </row>
     <row r="59">
@@ -24785,7 +24785,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no Opus assumptions file — every input is a builder default</t>
+          <t>seeded 2026-07-06 from the synced assumptions block (pass predates provenance tracking — may already include your edits)</t>
         </is>
       </c>
     </row>
@@ -24850,7 +24850,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -24858,7 +24858,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="31" t="inlineStr"/>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24877,7 +24881,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -24885,7 +24889,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr"/>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24904,7 +24912,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -24912,7 +24920,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="31" t="inlineStr"/>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24931,7 +24943,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -24939,7 +24951,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr"/>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24958,7 +24974,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -24966,7 +24982,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="31" t="inlineStr"/>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24985,7 +25005,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -24993,7 +25013,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr"/>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -25012,7 +25036,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -25020,7 +25044,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="31" t="inlineStr"/>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25039,7 +25067,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -25047,7 +25075,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="31" t="inlineStr"/>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25066,7 +25098,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -25074,7 +25106,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr"/>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25093,7 +25129,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -25101,7 +25137,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="31" t="inlineStr"/>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25120,7 +25160,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -25128,7 +25168,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="31" t="inlineStr"/>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25147,7 +25191,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -25155,7 +25199,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr"/>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25174,7 +25222,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -25182,7 +25230,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="31" t="inlineStr"/>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -25201,7 +25253,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -25209,7 +25261,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="31" t="inlineStr"/>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25228,7 +25284,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -25236,7 +25292,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="31" t="inlineStr"/>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -25255,7 +25315,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -25263,7 +25323,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="31" t="inlineStr"/>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25282,12 +25346,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>Opus</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.3x</t>
         </is>
       </c>
       <c r="F24" s="31" t="inlineStr"/>
@@ -25309,7 +25373,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -25317,7 +25381,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="31" t="inlineStr"/>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -25336,7 +25404,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">

--- a/dcf/PANW.xlsx
+++ b/dcf/PANW.xlsx
@@ -863,7 +863,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1119,25 +1119,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.06258496628528873</v>
+        <v>0.06258475102466118</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.06758496628528873</v>
+        <v>0.06758475102466119</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.07258496628528872</v>
+        <v>0.07258475102466118</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.07758496628528873</v>
+        <v>0.07758475102466118</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.08258496628528873</v>
+        <v>0.08258475102466119</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.08758496628528872</v>
+        <v>0.08758475102466118</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.09258496628528873</v>
+        <v>0.09258475102466118</v>
       </c>
     </row>
     <row r="5">
@@ -1145,25 +1145,25 @@
         <v>11.3</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>76.56378446538642</v>
+        <v>67.92525894725415</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>73.80705422911194</v>
+        <v>65.54189367943057</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>71.1803870278482</v>
+        <v>63.27045328336063</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>68.67692249703781</v>
+        <v>61.10504581999967</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>66.29019541904181</v>
+        <v>59.0401183733475</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>64.01411116304669</v>
+        <v>57.07043599098019</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>61.84292275946744</v>
+        <v>55.19106202559801</v>
       </c>
     </row>
     <row r="6">
@@ -1171,25 +1171,25 @@
         <v>12.3</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>80.65495136305209</v>
+        <v>71.42826083640023</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>77.71060087653947</v>
+        <v>68.88424843850242</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>74.90573472888306</v>
+        <v>66.46022776931963</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>72.23297881229223</v>
+        <v>64.14986700440959</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>69.6853843770707</v>
+        <v>61.94719921027279</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>67.25640156690879</v>
+        <v>59.84659965408419</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>64.93985471674343</v>
+        <v>57.84276462410057</v>
       </c>
     </row>
     <row r="7">
@@ -1197,25 +1197,25 @@
         <v>13.3</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>84.74611826071778</v>
+        <v>74.93126272554629</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>81.61414752396701</v>
+        <v>72.22660319757428</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>78.63108242991791</v>
+        <v>69.65000225527864</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>75.78903512754668</v>
+        <v>67.19468818881951</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>73.0805733350996</v>
+        <v>64.85428004719807</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>70.49869197077091</v>
+        <v>62.62276331718819</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>68.03678667401942</v>
+        <v>60.49446722260313</v>
       </c>
     </row>
     <row r="8">
@@ -1223,25 +1223,25 @@
         <v>14.3</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>88.83728515838345</v>
+        <v>78.43426461469237</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>85.51769417139452</v>
+        <v>75.56895795664613</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>82.35643013095277</v>
+        <v>72.83977674123763</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>79.34509144280111</v>
+        <v>70.23950937322942</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>76.47576229312848</v>
+        <v>67.76136088412335</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>73.74098237463301</v>
+        <v>65.39892698029217</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>71.13371863129542</v>
+        <v>63.14616982110568</v>
       </c>
     </row>
     <row r="9">
@@ -1249,25 +1249,25 @@
         <v>15.3</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>92.92845205604914</v>
+        <v>81.93726650383844</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>89.42124081882206</v>
+        <v>78.911312715718</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>86.08177783198764</v>
+        <v>76.02955122719663</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>82.90114775805554</v>
+        <v>73.28433055763935</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>79.87095125115738</v>
+        <v>70.66844172104864</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>76.98327277849512</v>
+        <v>68.17509064339617</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>74.23065058857142</v>
+        <v>65.79787241960823</v>
       </c>
     </row>
     <row r="10">
@@ -1275,25 +1275,25 @@
         <v>16.3</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>97.01961895371481</v>
+        <v>85.44026839298451</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>93.3247874662496</v>
+        <v>82.25366747478985</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>89.8071255330225</v>
+        <v>79.21932571315564</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>86.45720407330997</v>
+        <v>76.32915174204926</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>83.26614020918628</v>
+        <v>73.57552255797393</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>80.22556318235723</v>
+        <v>70.95125430650018</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>77.32758254584742</v>
+        <v>68.44957501811079</v>
       </c>
     </row>
     <row r="11">
@@ -1301,25 +1301,25 @@
         <v>17.3</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>101.1107858513805</v>
+        <v>88.94327028213058</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>97.22833411367714</v>
+        <v>85.5960222338617</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>93.53247323405736</v>
+        <v>82.40910019911465</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>90.0132603885644</v>
+        <v>79.37397292645917</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>86.66132916721517</v>
+        <v>76.4826033948992</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>83.46785358621936</v>
+        <v>73.72741796960418</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>80.42451450312339</v>
+        <v>71.10127761661333</v>
       </c>
     </row>
     <row r="13">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>348.0599975585938</v>
+        <v>346.9100036621094</v>
       </c>
     </row>
     <row r="14">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.07758496628528873</v>
+        <v>0.07758475102466118</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>14.3</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.7741892597276353</v>
+        <v>0.7802514589601112</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24456,7 +24456,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>348.0599975585938</v>
+        <v>346.9100036621094</v>
       </c>
     </row>
     <row r="49">
@@ -24466,7 +24466,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24618,13 +24618,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>79.34509144280111</v>
+        <v>70.23950937322942</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>109.4365782375633</v>
+        <v>94.36827091302737</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>57.18820422515071</v>
+        <v>51.97964602084913</v>
       </c>
     </row>
     <row r="59">
